--- a/uploads/UPLOAD-TEMPLATE/STORE-SALARIES-UPLOAD-TEMPLATE.xlsx
+++ b/uploads/UPLOAD-TEMPLATE/STORE-SALARIES-UPLOAD-TEMPLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\node proj\rest-api-nestjs\uploads\UPLOAD-TEMPLATE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OSH-Backend\uploads\UPLOAD-TEMPLATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8215D65B-F111-4C49-8320-3F6B61B359A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DB25FF-BB94-41DC-9589-A1A1E0817C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" xr2:uid="{8DE630E0-0B89-4DDE-A92E-DF514EA9A919}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8DE630E0-0B89-4DDE-A92E-DF514EA9A919}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>STORE NAME</t>
   </si>
@@ -39,9 +39,6 @@
     <t>CHOOKS EXP UC-LM CAMPUS</t>
   </si>
   <si>
-    <t>TAYUD LILOAN</t>
-  </si>
-  <si>
     <t>AGENCY CODE</t>
   </si>
   <si>
@@ -73,6 +70,12 @@
   </si>
   <si>
     <t>CITI HRM CORP</t>
+  </si>
+  <si>
+    <t>MEMBER</t>
+  </si>
+  <si>
+    <t>WALTERMART SUPERMARKET, INC. - TAYTAY</t>
   </si>
 </sst>
 </file>
@@ -439,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE589B1-C7BA-44D4-9E29-919A5892AA9B}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -452,25 +455,25 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -484,13 +487,13 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
         <v>46188</v>
@@ -499,7 +502,7 @@
         <v>695</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -510,13 +513,13 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2">
         <v>46188</v>
@@ -529,29 +532,314 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>50000610</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F50" s="2"/>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F51" s="2"/>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F52" s="2"/>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F53" s="2"/>
+    </row>
+    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F54" s="2"/>
+    </row>
+    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F56" s="2"/>
+    </row>
+    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F59" s="2"/>
+    </row>
+    <row r="60" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F63" s="2"/>
+    </row>
+    <row r="64" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F66" s="2"/>
+    </row>
+    <row r="67" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F67" s="2"/>
+    </row>
+    <row r="68" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F71" s="2"/>
+    </row>
+    <row r="72" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F72" s="2"/>
+    </row>
+    <row r="73" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F73" s="2"/>
+    </row>
+    <row r="74" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F74" s="2"/>
+    </row>
+    <row r="75" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F75" s="2"/>
+    </row>
+    <row r="76" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F76" s="2"/>
+    </row>
+    <row r="77" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F77" s="2"/>
+    </row>
+    <row r="78" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F78" s="2"/>
+    </row>
+    <row r="79" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F79" s="2"/>
+    </row>
+    <row r="80" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F80" s="2"/>
+    </row>
+    <row r="81" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F81" s="2"/>
+    </row>
+    <row r="82" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F82" s="2"/>
+    </row>
+    <row r="83" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F83" s="2"/>
+    </row>
+    <row r="84" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F84" s="2"/>
+    </row>
+    <row r="85" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F85" s="2"/>
+    </row>
+    <row r="86" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F86" s="2"/>
+    </row>
+    <row r="87" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F87" s="2"/>
+    </row>
+    <row r="88" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F88" s="2"/>
+    </row>
+    <row r="89" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F89" s="2"/>
+    </row>
+    <row r="90" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F90" s="2"/>
+    </row>
+    <row r="91" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F91" s="2"/>
+    </row>
+    <row r="92" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F92" s="2"/>
+    </row>
+    <row r="93" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F93" s="2"/>
+    </row>
+    <row r="94" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F94" s="2"/>
+    </row>
+    <row r="95" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F95" s="2"/>
+    </row>
+    <row r="96" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F96" s="2"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F97" s="2"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F98" s="2"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>10002529</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E99" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="F99" s="2">
         <v>46188</v>
       </c>
-      <c r="G4">
+      <c r="G99">
         <v>695</v>
       </c>
-      <c r="H4" t="s">
-        <v>11</v>
+      <c r="H99" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
